--- a/artfynd/A 68385-2021 artfynd.xlsx
+++ b/artfynd/A 68385-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68385-2021 artfynd.xlsx
+++ b/artfynd/A 68385-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96092425</v>
+        <v>110285230</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Tjähppsåijvve, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699660.4371019853</v>
+        <v>700025</v>
       </c>
       <c r="R2" t="n">
-        <v>7309638.715581233</v>
+        <v>7309460</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,55 +761,81 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>på död toppbruten gammal gran</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # på död toppbruten gammal gran # Picea abies subsp. abies # på död toppbruten gammal gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96092084</v>
+        <v>96092361</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,34 +843,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>avverkningsanmält skog Tjappsberget, Pi lm</t>
+          <t>Tjappsberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699908.657810635</v>
+        <v>700029</v>
       </c>
       <c r="R3" t="n">
-        <v>7309465.794195623</v>
+        <v>7309573</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,56 +922,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103620046</v>
+        <v>110285322</v>
       </c>
       <c r="B4" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjappsberget, Pi lm</t>
+          <t>Tjähppsåijvve, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699969.2695698005</v>
+        <v>700020</v>
       </c>
       <c r="R4" t="n">
-        <v>7309334.415684144</v>
+        <v>7309575</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,27 +1015,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103620574</v>
+        <v>110285190</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,40 +1038,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjappsberget, Pi lm</t>
+          <t>Tjähppsåijvve, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699969.2695698005</v>
+        <v>700035</v>
       </c>
       <c r="R5" t="n">
-        <v>7309334.415684144</v>
+        <v>7309420</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1099,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,27 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103620607</v>
+        <v>110285333</v>
       </c>
       <c r="B6" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,40 +1143,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjappsberget, Pi lm</t>
+          <t>Tjähppsåijvve, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699969.2695698005</v>
+        <v>699905</v>
       </c>
       <c r="R6" t="n">
-        <v>7309334.415684144</v>
+        <v>7309580</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,22 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,27 +1225,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103601354</v>
+        <v>112183052</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,38 +1248,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Arvidsjaur, Pi lm</t>
+          <t>Tjappsåive, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699844.2727480198</v>
+        <v>699857</v>
       </c>
       <c r="R7" t="n">
-        <v>7309557.043342081</v>
+        <v>7309603</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1338,22 +1306,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2023-08-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,27 +1331,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103619429</v>
+        <v>110285152</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,37 +1354,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjappsberget, Pi lm</t>
+          <t>Tjähppsåijvve, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699959.0462449663</v>
+        <v>700040</v>
       </c>
       <c r="R8" t="n">
-        <v>7309433.564056673</v>
+        <v>7309310</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,22 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,49 +1436,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110285141</v>
+        <v>110285159</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1543,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>700020.4497028914</v>
+        <v>700030</v>
       </c>
       <c r="R9" t="n">
-        <v>7309320.322768679</v>
+        <v>7309385</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,19 +1523,9 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,15 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110285342</v>
+        <v>110285300</v>
       </c>
       <c r="B10" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,31 +1564,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1664,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699905.2147470837</v>
+        <v>700065</v>
       </c>
       <c r="R10" t="n">
-        <v>7309579.794423973</v>
+        <v>7309495</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,32 +1628,18 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack i gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1741,15 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110285190</v>
+        <v>110285313</v>
       </c>
       <c r="B11" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,27 +1669,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1788,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>700035.2562240658</v>
+        <v>700040</v>
       </c>
       <c r="R11" t="n">
-        <v>7309420.400305547</v>
+        <v>7309565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,19 +1733,9 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,37 +1763,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110285152</v>
+        <v>110284979</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1908,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>700040.4652493782</v>
+        <v>699970</v>
       </c>
       <c r="R12" t="n">
-        <v>7309310.626369719</v>
+        <v>7309285</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,19 +1838,9 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,15 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110285333</v>
+        <v>103620046</v>
       </c>
       <c r="B13" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,44 +1879,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjähppsåijvve, Pi lm</t>
+          <t>Tjappsberget, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699905.2147470837</v>
+        <v>699969</v>
       </c>
       <c r="R13" t="n">
-        <v>7309579.794423973</v>
+        <v>7309335</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2058,22 +1936,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,62 +1957,53 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110285162</v>
+        <v>110284969</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2152,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>700029.4704191192</v>
+        <v>699870</v>
       </c>
       <c r="R14" t="n">
-        <v>7309385.475161105</v>
+        <v>7309530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,24 +2044,9 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fertil!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,37 +2074,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110285159</v>
+        <v>110285141</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2277,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>700029.4704191192</v>
+        <v>700020</v>
       </c>
       <c r="R15" t="n">
-        <v>7309385.475161105</v>
+        <v>7309320</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,19 +2149,9 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,60 +2179,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110285313</v>
+        <v>103601354</v>
       </c>
       <c r="B16" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tjähppsåijvve, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>700040.3931685599</v>
+        <v>699844</v>
       </c>
       <c r="R16" t="n">
-        <v>7309564.590576654</v>
+        <v>7309557</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2427,22 +2245,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2451,56 +2269,50 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110285472</v>
+        <v>110284945</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2517,13 +2329,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>700051.6114032021</v>
+        <v>699825</v>
       </c>
       <c r="R17" t="n">
-        <v>7309539.486218478</v>
+        <v>7309535</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2550,19 +2362,9 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2590,19 +2392,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110284945</v>
+        <v>110285162</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2629,7 +2426,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2637,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699824.8507061265</v>
+        <v>700030</v>
       </c>
       <c r="R18" t="n">
-        <v>7309534.728627129</v>
+        <v>7309385</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2670,19 +2471,14 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fertil!</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2710,60 +2506,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110284969</v>
+        <v>103620607</v>
       </c>
       <c r="B19" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4217</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tjähppsåijvve, Pi lm</t>
+          <t>Tjappsberget, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699869.5803223751</v>
+        <v>699969</v>
       </c>
       <c r="R19" t="n">
-        <v>7309530.457412811</v>
+        <v>7309335</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2787,22 +2574,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,27 +2595,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110285300</v>
+        <v>96092425</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2846,44 +2618,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjähppsåijvve, Pi lm</t>
+          <t>Arvidsjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>700065.0217598052</v>
+        <v>699660</v>
       </c>
       <c r="R20" t="n">
-        <v>7309494.809666311</v>
+        <v>7309639</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2907,22 +2673,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,34 +2697,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110285230</v>
+        <v>110285472</v>
       </c>
       <c r="B21" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2966,27 +2726,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2997,13 +2757,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>700024.6457686943</v>
+        <v>700052</v>
       </c>
       <c r="R21" t="n">
-        <v>7309460.342548816</v>
+        <v>7309540</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3030,19 +2790,9 @@
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-06-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,36 +2804,6 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>på död toppbruten gammal gran</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # på död toppbruten gammal gran # Picea abies subsp. abies # på död toppbruten gammal gran</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3100,57 +2820,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112183052</v>
+        <v>103600394</v>
       </c>
       <c r="B22" t="n">
-        <v>77770</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tjappsåive, Pi lm</t>
+          <t>Tjappsberget , Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699857</v>
+        <v>699574</v>
       </c>
       <c r="R22" t="n">
-        <v>7309603</v>
+        <v>7309730</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3174,17 +2886,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-08-17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3199,15 +2916,457 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110284889</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tjähppsåijvve, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>699580</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7309725</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>110285342</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tjähppsåijvve, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>699905</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7309580</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Hack i gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>96092084</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>avverkningsanmält skog Tjappsberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>699909</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7309466</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-09-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-09-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>103620574</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tjappsberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>699969</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7309335</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
